--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England Premier League_20242025.xlsx
@@ -16422,13 +16422,13 @@
         <v>10</v>
       </c>
       <c r="BA73" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB73" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BC73" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="BD73" t="n">
         <v>1.84</v>
@@ -16640,13 +16640,13 @@
         <v>6</v>
       </c>
       <c r="BA74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB74" t="n">
         <v>2</v>
       </c>
       <c r="BC74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD74" t="n">
         <v>1.36</v>
@@ -17079,10 +17079,10 @@
         <v>10</v>
       </c>
       <c r="BB76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD76" t="n">
         <v>1.52</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/England Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/England Premier League_20242025.xlsx
@@ -81592,16 +81592,16 @@
         <v>6</v>
       </c>
       <c r="AW372" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX372" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY372" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ372" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA372" t="n">
         <v>4</v>
@@ -81810,13 +81810,13 @@
         <v>0</v>
       </c>
       <c r="AW373" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX373" t="n">
         <v>3</v>
       </c>
       <c r="AY373" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ373" t="n">
         <v>3</v>
@@ -82028,16 +82028,16 @@
         <v>1</v>
       </c>
       <c r="AW374" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX374" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY374" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ374" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA374" t="n">
         <v>4</v>
@@ -82246,16 +82246,16 @@
         <v>6</v>
       </c>
       <c r="AW375" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX375" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY375" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ375" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA375" t="n">
         <v>12</v>
@@ -82464,16 +82464,16 @@
         <v>2</v>
       </c>
       <c r="AW376" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX376" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY376" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ376" t="n">
         <v>4</v>
-      </c>
-      <c r="AY376" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ376" t="n">
-        <v>6</v>
       </c>
       <c r="BA376" t="n">
         <v>7</v>
@@ -82682,16 +82682,16 @@
         <v>8</v>
       </c>
       <c r="AW377" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX377" t="n">
         <v>5</v>
       </c>
-      <c r="AX377" t="n">
-        <v>15</v>
-      </c>
       <c r="AY377" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ377" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA377" t="n">
         <v>5</v>
@@ -82900,16 +82900,16 @@
         <v>8</v>
       </c>
       <c r="AW378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX378" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY378" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ378" t="n">
         <v>15</v>
-      </c>
-      <c r="AY378" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ378" t="n">
-        <v>23</v>
       </c>
       <c r="BA378" t="n">
         <v>2</v>
@@ -83118,16 +83118,16 @@
         <v>7</v>
       </c>
       <c r="AW379" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX379" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY379" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ379" t="n">
         <v>12</v>
-      </c>
-      <c r="AX379" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY379" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ379" t="n">
-        <v>13</v>
       </c>
       <c r="BA379" t="n">
         <v>8</v>
@@ -83336,16 +83336,16 @@
         <v>5</v>
       </c>
       <c r="AW380" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX380" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AY380" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ380" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BA380" t="n">
         <v>1</v>
@@ -83554,16 +83554,16 @@
         <v>5</v>
       </c>
       <c r="AW381" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY381" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ381" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA381" t="n">
         <v>11</v>
